--- a/rodier-finding-llama3.2-bert-scores.xlsx
+++ b/rodier-finding-llama3.2-bert-scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>DOCUMENT</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
   </si>
   <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
     <t xml:space="preserve">The deceased was Frank Edward Rodier </t>
   </si>
   <si>
@@ -124,59 +127,70 @@
     <t xml:space="preserve">Not applicable in this case; the death occurred during a recreational activity at sea, not under institutional supervision or care </t>
   </si>
   <si>
+    <t>Yes. The Rodier case underscores a broader public safety lesson about the persistent dangers of rock fishing and the need for preventive measures at hazardous coastal sites. The coroner observed that while Western Australia has since introduced safety improvements such as life rings and tether points at popular rock fishing locations, remote areas like Quobba Station remain perilous and largely unmonitored. The finding highlights how environmental risks, rather than institutional failures, were central, emphasizing the importance of sustained public education, signage, and infrastructure to reduce fatalities from recreational fishing accidents</t>
+  </si>
+  <si>
     <t>The deceased person was Frank Edward RODIER.</t>
   </si>
   <si>
-    <t>The death occurred on November 25, 1975.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, it is stated that the death of Frank Rodier occurred in the waters of the Indian Ocean off Quobba Station near Red Bluff, Carnarvon.</t>
-  </si>
-  <si>
-    <t>The cause of death cannot be determined with certainty due to insufficient evidence. However, it is believed that Frank Rodier may have died from injuries sustained from being washed off rocks while fishing, which could have contributed to his death. The manner of death remains unascertained, but it appears he died by accident.</t>
-  </si>
-  <si>
-    <t>The presiding coroner in this case was Deputy State Coroner Sarah Helen Linton.</t>
-  </si>
-  <si>
-    <t>According to the context information, Frank Rodier died in the sea on 25th March 1975 (not 25 1975) after being washed off rocks while fishing with friends. The exact cause of his death cannot be determined beyond reasonable doubt, but it is believed that he may have sustained injuries from the rocks, which could have contributed to his death. However, the manner of death was confirmed as an accident.</t>
-  </si>
-  <si>
-    <t>According to the provided context information, Frank had some slight impairments, specifically related to speech. This is mentioned in the background section of the report as one of the only notable physical or health issues he experienced.</t>
-  </si>
-  <si>
-    <t>According to the context information, the following individuals testified or assisted in the inquest:
-1. Detective Sergeant Ellie Wold from the Homicide Squad Missing Person Team
-2. Senior Constable C Robertson (who assisted the Coroner)</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, there is no indication that the deceased was considered a "person held in care" under the Coroners Act. The coroner's decision to investigate the death as a reportable death suggests that the death may have occurred in custody or under circumstances where the coroner's inquiry is required, but it does not explicitly state that the person was held in care.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, I can only provide a summary of the available data, but without direct access to the report, I cannot confirm specific toxicology findings. 
-However, it is mentioned that there was reasonable cause to suspect that Frank had died and that his death was reportable under the Act, which led to an investigation being conducted by the police.</t>
-  </si>
-  <si>
-    <t>The Acting State Coroner determined that there was reasonable cause to suspect Frank's death was reportable under the Act. As a result, they made a direction for the suspected death to be investigated by the Commissioner of Police. This investigation was prompted by information provided by the WA Police in August 2023.</t>
-  </si>
-  <si>
-    <t>Based on the provided context information, there is no indication that the coroner made any recommendations for future prevention. The decision appears to be focused solely on investigating Frank's death and determining whether it was a reportable death under the Act, with no mention of preventive measures or recommendations.</t>
-  </si>
-  <si>
-    <t>Based on the provided context, here's a differentiation between the immediate cause of death and contributing factors:
+    <t>Based on the provided context information, Frank Rodier died on November 25, 1975.</t>
+  </si>
+  <si>
+    <t>The location where the death occurred is in the waters of the Indian Ocean off Quobba Station near Red Bluff, Carnarvon. Specifically, the incident happened at the Caves area, 75 miles north of Carnarvon.</t>
+  </si>
+  <si>
+    <t>The cause of death cannot be determined with certainty due to a lack of clear evidence. It is possible that Frank Rodier died from injuries sustained from the rocks or that injury contributed to his death, but it remains unascertained.</t>
+  </si>
+  <si>
+    <t>The presiding coroner in this case was Sarah Helen Linton, who acted as the Deputy State Coroner.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it appears that Frank Rodier died as a result of being washed off rocks while fishing with friends. The exact circumstances surrounding his death are unclear, but it is believed that he may have sustained injuries from the rocks before or during the incident, which could have contributed to his death.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it is stated that Frank had "some slight impairments" which affected his speech. No other specific medical or mental health conditions are mentioned as being present.</t>
+  </si>
+  <si>
+    <t>According to the provided context information, one person testified:
+1. Detective Sergeant Ellie Wold (from the Homicide Squad Missing Person Team)
+2. Senior Constable C Robertson assisted the Coroner.
+There is no mention of anyone else testifying or assisting in the inquest.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, it is unclear whether Frank was specifically described as a "person held in care" in the decision or report. The information only mentions that there was reasonable cause to suspect Frank had died and that his death was a reportable death under the Act, but does not explicitly state that he was held in care at the time of his death.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, I can only infer that a toxicology report was conducted as part of the investigation into Frank's death. However, without access to the actual toxicology report, I cannot provide specific details about the presence or absence of substances or drugs in Frank's body.
+Therefore, I must answer "No" to the question, indicating that there is no available information in this context regarding toxicology findings.</t>
+  </si>
+  <si>
+    <t>The Acting State Coroner determined that there was reasonable cause to suspect Frank's death, specifically that his death was a reportable death under the Act. The coroner made a direction for the Commissioner of Police to investigate the suspected death. As a result, an investigation was launched in August 2023.</t>
+  </si>
+  <si>
+    <t>Yes, the coroner made a direction to the Commissioner of Police pursuant to s 23(1) of the Coroners Act 1996 (WA), which implies that they may have also made recommendations for future prevention of similar reportable deaths. However, the provided context information does not explicitly mention any specific recommendations for future prevention.
+The coroner's decision only mentions an investigation into Frank's suspected death and a direction to the Commissioner of Police. It does not provide details on any preventive measures or recommendations that were made as part of their ruling.</t>
+  </si>
+  <si>
+    <t>Based on the provided context information, here's a differentiation between the immediate cause of death and contributing factors:
 Immediate Cause of Death:
-The immediate cause of Frank Rodier's death is likely to be drowning in the sea after being washed off the rocks while fishing. This can be inferred from the fact that he was found dead at the scene and died on August 25, 1975.
+The coroner is satisfied that Frank died from drowning in the sea, specifically after being washed off the rocks while fishing with friends.
 Contributing Factors:
-There are two contributing factors mentioned in the context:
-1. Injuries sustained from the rocks: It is possible that Frank Rodier's death was caused or contributed to by injuries he sustained from the rocks while fishing. Although it is not clear if these injuries were the sole cause of death, they could have played a role in his demise.
-2. Accidental injuries at birth: There is also an indication that Frank Rodier may have had accidental injuries associated with events at the time of his birth, but no further details are provided about their relationship to his death.
-In summary, while drowning is likely the immediate cause of Frank Rodier's death, there could be other contributing factors such as injuries from the rocks and accidents during birth. The exact nature and extent of these contributions remain unclear based on the provided context.</t>
-  </si>
-  <si>
-    <t>Based on the given context information, it appears that the coroner did not explicitly evaluate the adequacy of supervision, treatment, or care provided in this case. However, we can make an inference based on the following:
-* The coroner made a direction for the Commissioner of Police to investigate, as there was reasonable cause to suspect that Frank had died and his death was reportable.
-* There is no mention of any evaluation of the adequacy of supervision, treatment, or care provided prior to Frank's death.
-Therefore, it can be concluded that the coroner did not evaluate the adequacy of supervision, treatment, or care provided in this case.</t>
+While the coroner is not entirely certain about the role of injuries sustained from the rocks, it is possible that these injuries contributed to his death. Therefore, the coroner cannot exclude the possibility that the injury(s) played a part in Frank's death.
+In other words:
+* Immediate cause of death: Drowning due to being washed off the rocks while fishing.
+* Contributing factors: Potential role of injuries sustained from the rocks, which may have contributed to his death.</t>
+  </si>
+  <si>
+    <t>Based on the context information, it appears that the coroner did not specifically address the evaluation of the adequacy of supervision, treatment, or care provided. The coroner only mentioned that there was reasonable cause to suspect Frank's death and made a direction for the suspected death to be investigated.
+However, since the investigation is now underway (as indicated by the involvement of Senior Constable C Robertson), it can be inferred that such an evaluation may have been part of the initial assessment or will likely be considered as part of the ongoing investigation. The coroner's primary concern at this point appears to be the investigation itself, rather than evaluating specific care provided prior to Frank's death.</t>
+  </si>
+  <si>
+    <t>Yes, this case highlights several broader patterns and lessons relevant to public safety and institutional care. Some of these include:
+1. The importance of thorough and timely investigations into missing persons cases: The fact that Frank's disappearance was not initially treated as a suspicious death until 2023 suggests that there may have been missed opportunities for investigation or communication with the family.
+2. The need for effective communication between law enforcement agencies, coroners' offices, and families: The case involved multiple reviews of Frank's disappearance over several decades, with different outcomes at each stage. This highlights the importance of clear communication and coordination across these organizations to ensure that cases are handled appropriately.
+3. The impact of institutional failures on individual safety: Frank's death appears to have been the result of a combination of factors, including his age, health status, and likely lack of supervision while out in the community. This suggests that older adults or vulnerable populations may be disproportionately affected by institutional failures.
+4. The role of coroners' inquiries in ensuring public safety: As Acting State Coroner, the author of the decision played a crucial role in investigating Frank's death and identifying potential causes. This highlights the importance of coroners' offices in holding institutions accountable for their actions and ensuring that lessons are learned from tragic events.
+5. The need for ongoing support and resources for families affected by missing persons cases: The case involved multiple reviews over several decades, with no resolution until 2023. This suggests that families may require ongoing support and resources to cope with the uncertainty and lack of closure that can accompany a missing person's case.</t>
   </si>
 </sst>
 </file>
@@ -534,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -568,10 +582,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0.9367325305938721</v>
@@ -591,19 +605,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>0.8710184097290039</v>
+        <v>0.8248656392097473</v>
       </c>
       <c r="F3">
-        <v>0.850217342376709</v>
+        <v>0.8424435257911682</v>
       </c>
       <c r="G3">
-        <v>0.8604921698570251</v>
+        <v>0.833561897277832</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -614,19 +628,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>0.8831475973129272</v>
+        <v>0.8735595941543579</v>
       </c>
       <c r="F4">
-        <v>0.95506751537323</v>
+        <v>0.9407526850700378</v>
       </c>
       <c r="G4">
-        <v>0.9177005887031555</v>
+        <v>0.905911922454834</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -637,19 +651,19 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>0.8592415452003479</v>
+        <v>0.8590243458747864</v>
       </c>
       <c r="F5">
-        <v>0.879115879535675</v>
+        <v>0.8840421438217163</v>
       </c>
       <c r="G5">
-        <v>0.8690651059150696</v>
+        <v>0.8713536858558655</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -660,19 +674,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0.8995692729949951</v>
+        <v>0.8855115175247192</v>
       </c>
       <c r="F6">
-        <v>0.9280666708946228</v>
+        <v>0.9294424057006836</v>
       </c>
       <c r="G6">
-        <v>0.9135957956314087</v>
+        <v>0.9069452881813049</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -683,19 +697,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>0.8582758903503418</v>
+        <v>0.86842942237854</v>
       </c>
       <c r="F7">
-        <v>0.8652727603912354</v>
+        <v>0.8566746711730957</v>
       </c>
       <c r="G7">
-        <v>0.861760139465332</v>
+        <v>0.8625120520591736</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -706,19 +720,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>0.8489882946014404</v>
+        <v>0.857719361782074</v>
       </c>
       <c r="F8">
-        <v>0.8589474558830261</v>
+        <v>0.8624783754348755</v>
       </c>
       <c r="G8">
-        <v>0.8539388179779053</v>
+        <v>0.8600922822952271</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -729,19 +743,19 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>0.8575494289398193</v>
+        <v>0.850895881652832</v>
       </c>
       <c r="F9">
-        <v>0.8908788561820984</v>
+        <v>0.8894413709640503</v>
       </c>
       <c r="G9">
-        <v>0.8738964200019836</v>
+        <v>0.8697417378425598</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -752,19 +766,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10">
-        <v>0.8358203172683716</v>
+        <v>0.8408839702606201</v>
       </c>
       <c r="F10">
-        <v>0.8698809146881104</v>
+        <v>0.8586511611938477</v>
       </c>
       <c r="G10">
-        <v>0.8525105118751526</v>
+        <v>0.8496747016906738</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -775,19 +789,19 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11">
-        <v>0.8277177810668945</v>
+        <v>0.8279709219932556</v>
       </c>
       <c r="F11">
-        <v>0.8851944208145142</v>
+        <v>0.8795076012611389</v>
       </c>
       <c r="G11">
-        <v>0.8554918169975281</v>
+        <v>0.8529614806175232</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -798,19 +812,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12">
-        <v>0.8384833335876465</v>
+        <v>0.8501685857772827</v>
       </c>
       <c r="F12">
-        <v>0.8272956609725952</v>
+        <v>0.8273904323577881</v>
       </c>
       <c r="G12">
-        <v>0.8328518867492676</v>
+        <v>0.838624894618988</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -821,19 +835,19 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13">
-        <v>0.8503557443618774</v>
+        <v>0.8281615972518921</v>
       </c>
       <c r="F13">
-        <v>0.8515579700469971</v>
+        <v>0.8453732132911682</v>
       </c>
       <c r="G13">
-        <v>0.8509564399719238</v>
+        <v>0.8366788625717163</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -844,19 +858,19 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>0.8124254941940308</v>
+        <v>0.8206738233566284</v>
       </c>
       <c r="F14">
-        <v>0.8370692729949951</v>
+        <v>0.8391966819763184</v>
       </c>
       <c r="G14">
-        <v>0.8245632648468018</v>
+        <v>0.8298318982124329</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -867,19 +881,42 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>0.8265010714530945</v>
+        <v>0.8186550140380859</v>
       </c>
       <c r="F15">
-        <v>0.8523151278495789</v>
+        <v>0.8422983884811401</v>
       </c>
       <c r="G15">
-        <v>0.8392096161842346</v>
+        <v>0.8303083777427673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>0.8258551359176636</v>
+      </c>
+      <c r="F16">
+        <v>0.847109317779541</v>
+      </c>
+      <c r="G16">
+        <v>0.836347222328186</v>
       </c>
     </row>
   </sheetData>
